--- a/data/trans_dic/P16-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,34; 45,25</t>
+          <t>33,84; 45,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,38; 62,93</t>
+          <t>51,16; 62,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,7; 64,86</t>
+          <t>53,05; 64,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,28; 71,15</t>
+          <t>57,23; 71,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,58; 65,15</t>
+          <t>52,24; 65,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,34; 82,72</t>
+          <t>71,86; 82,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,29; 75,2</t>
+          <t>63,44; 74,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,62; 78,88</t>
+          <t>69,13; 78,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,54; 53,53</t>
+          <t>44,92; 53,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,89; 71,02</t>
+          <t>63,11; 71,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60,33; 68,63</t>
+          <t>59,96; 68,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,06; 73,66</t>
+          <t>65,35; 73,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,02; 43,31</t>
+          <t>34,03; 42,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 55,98</t>
+          <t>46,8; 55,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,85; 53,3</t>
+          <t>43,56; 52,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,44; 55,3</t>
+          <t>43,7; 55,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,75; 62,47</t>
+          <t>54,09; 63,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,77; 75,45</t>
+          <t>67,62; 75,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,64; 70,84</t>
+          <t>62,74; 70,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,14; 68,26</t>
+          <t>60,59; 68,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,23; 51,84</t>
+          <t>45,47; 51,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,15; 64,68</t>
+          <t>58,5; 64,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,45; 60,71</t>
+          <t>54,58; 61,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,36; 60,93</t>
+          <t>53,37; 60,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,34; 41,87</t>
+          <t>31,14; 42,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,38; 59,49</t>
+          <t>48,09; 59,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,33; 56,34</t>
+          <t>45,12; 55,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,44; 64,08</t>
+          <t>52,59; 63,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,08; 66,65</t>
+          <t>55,94; 66,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,89; 80,58</t>
+          <t>70,78; 80,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,06; 70,47</t>
+          <t>59,85; 70,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,99; 73,55</t>
+          <t>65,11; 73,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,01; 52,99</t>
+          <t>45,21; 52,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61,29; 68,82</t>
+          <t>61,65; 69,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,83; 62,08</t>
+          <t>54,71; 62,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,9; 67,92</t>
+          <t>60,13; 67,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,8; 45,47</t>
+          <t>35,15; 44,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,27; 54,24</t>
+          <t>44,23; 54,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,17; 66,28</t>
+          <t>55,75; 65,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,51; 64,25</t>
+          <t>49,53; 64,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,58; 62,4</t>
+          <t>52,98; 62,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,12; 78,8</t>
+          <t>70,07; 78,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,16; 78,83</t>
+          <t>69,66; 78,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,24; 78,2</t>
+          <t>53,02; 77,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,83; 52,52</t>
+          <t>45,36; 52,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,19; 65,8</t>
+          <t>58,07; 65,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64,43; 71,54</t>
+          <t>64,45; 71,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,24; 71,82</t>
+          <t>54,73; 71,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,37; 53,5</t>
+          <t>39,96; 54,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,52; 60,48</t>
+          <t>46,35; 60,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,57; 49,83</t>
+          <t>36,26; 50,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,39; 55,22</t>
+          <t>42,39; 55,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,97; 69,52</t>
+          <t>56,36; 69,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,86; 86,65</t>
+          <t>75,55; 86,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,61; 70,7</t>
+          <t>58,14; 71,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,94; 68,99</t>
+          <t>59,74; 69,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,15; 59,95</t>
+          <t>50,06; 60,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,06; 72,13</t>
+          <t>63,14; 72,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,7; 58,83</t>
+          <t>49,89; 59,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,42; 61,02</t>
+          <t>52,71; 61,07</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,77; 46,4</t>
+          <t>34,37; 45,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,95; 64,76</t>
+          <t>52,4; 64,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,76; 52,33</t>
+          <t>39,87; 52,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,83; 63,65</t>
+          <t>52,8; 63,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,95; 70,19</t>
+          <t>58,49; 69,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,87; 82,52</t>
+          <t>72,96; 82,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,46; 69,09</t>
+          <t>57,64; 68,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,93; 69,74</t>
+          <t>59,24; 69,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,46; 57,09</t>
+          <t>48,38; 57,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,69; 72,71</t>
+          <t>64,48; 72,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50,53; 59,27</t>
+          <t>50,68; 59,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57,49; 65,25</t>
+          <t>57,85; 65,12</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,75; 43,17</t>
+          <t>34,9; 43,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,38; 56,62</t>
+          <t>47,99; 56,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,38; 49,71</t>
+          <t>40,93; 49,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,26; 64,83</t>
+          <t>55,09; 65,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,78; 59,75</t>
+          <t>51,59; 59,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,73; 71,46</t>
+          <t>63,87; 71,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,11; 61,1</t>
+          <t>53,5; 60,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,52; 87,9</t>
+          <t>67,63; 88,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,51; 50,4</t>
+          <t>44,72; 49,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,12; 62,62</t>
+          <t>57,28; 62,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48,36; 54,21</t>
+          <t>48,35; 54,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,72; 81,13</t>
+          <t>63,53; 79,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,03; 48,28</t>
+          <t>40,83; 47,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,08; 45,7</t>
+          <t>37,9; 45,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,91; 52,2</t>
+          <t>44,82; 52,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,88; 39,9</t>
+          <t>12,72; 39,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,96; 60,63</t>
+          <t>53,01; 59,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,65; 62,48</t>
+          <t>55,18; 61,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,54; 67,3</t>
+          <t>60,66; 67,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,52; 54,74</t>
+          <t>48,64; 55,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,17; 53,27</t>
+          <t>48,23; 53,28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,92; 52,94</t>
+          <t>47,88; 53,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53,72; 58,9</t>
+          <t>53,82; 58,77</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,2; 45,99</t>
+          <t>23,55; 46,2</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,87; 42,28</t>
+          <t>39,03; 42,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48,74; 52,14</t>
+          <t>48,51; 52,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48,13; 51,57</t>
+          <t>48,07; 51,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37,87; 53,75</t>
+          <t>38,23; 53,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,74; 60,35</t>
+          <t>56,87; 60,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,64; 71,83</t>
+          <t>68,7; 71,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,99; 66,46</t>
+          <t>63,38; 66,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63,35; 73,24</t>
+          <t>63,1; 71,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48,45; 50,88</t>
+          <t>48,47; 50,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59,2; 61,66</t>
+          <t>59,37; 61,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56,35; 58,79</t>
+          <t>56,3; 58,65</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,05; 61,46</t>
+          <t>51,84; 61,58</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91021; 123538</t>
+          <t>92374; 123987</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>147605; 184382</t>
+          <t>149910; 184168</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154820; 190548</t>
+          <t>155839; 189302</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178388; 221602</t>
+          <t>178244; 221576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>137154; 169938</t>
+          <t>136264; 169827</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>207787; 237605</t>
+          <t>206403; 236981</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>185620; 217103</t>
+          <t>183163; 214976</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>198755; 228475</t>
+          <t>200210; 228296</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>237768; 285752</t>
+          <t>239817; 285012</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>364946; 412100</t>
+          <t>366205; 412608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>351424; 399728</t>
+          <t>349229; 396714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>391077; 442756</t>
+          <t>392811; 442599</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>167740; 213552</t>
+          <t>167795; 211242</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>235824; 283004</t>
+          <t>236584; 282648</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220354; 267859</t>
+          <t>218938; 266306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230367; 286655</t>
+          <t>226551; 286477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>270874; 314797</t>
+          <t>272596; 317656</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>354272; 394410</t>
+          <t>353452; 396379</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>327673; 370579</t>
+          <t>328196; 370044</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>309310; 351040</t>
+          <t>311624; 352711</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>450971; 516827</t>
+          <t>453334; 517113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>597897; 665057</t>
+          <t>601505; 664426</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>558442; 622709</t>
+          <t>559791; 626653</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>551083; 629184</t>
+          <t>551150; 624153</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99922; 133499</t>
+          <t>99288; 134150</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>156321; 192212</t>
+          <t>155386; 192176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144412; 179464</t>
+          <t>143737; 177781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165744; 202519</t>
+          <t>166216; 202176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>188113; 223557</t>
+          <t>187622; 222820</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>241746; 274797</t>
+          <t>241378; 274814</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>201980; 237006</t>
+          <t>201273; 238682</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>226901; 256769</t>
+          <t>227317; 257553</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>294514; 346673</t>
+          <t>295779; 345533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>407067; 457072</t>
+          <t>409437; 459226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359083; 406556</t>
+          <t>358253; 406537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>405094; 451820</t>
+          <t>399940; 450086</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>124814; 163081</t>
+          <t>126058; 160936</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161835; 202861</t>
+          <t>165406; 203138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>207823; 245204</t>
+          <t>206268; 244027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>154740; 200829</t>
+          <t>154811; 202382</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>195317; 231788</t>
+          <t>196805; 233454</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>272043; 305714</t>
+          <t>271872; 305170</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>271718; 305304</t>
+          <t>269780; 305037</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>253259; 371993</t>
+          <t>252209; 370893</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>327326; 383440</t>
+          <t>331156; 385107</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>443386; 501357</t>
+          <t>442434; 497207</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>487921; 541745</t>
+          <t>488019; 540540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>427576; 566124</t>
+          <t>431461; 567050</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82086; 108765</t>
+          <t>81248; 109889</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98917; 128597</t>
+          <t>98542; 128783</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77246; 105257</t>
+          <t>76588; 105933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75760; 98698</t>
+          <t>75764; 98414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>116233; 144367</t>
+          <t>117049; 145216</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>166585; 190276</t>
+          <t>165906; 188964</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>128116; 154538</t>
+          <t>127096; 155301</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>125068; 143951</t>
+          <t>124643; 144370</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206118; 246374</t>
+          <t>205753; 246946</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>272537; 311748</t>
+          <t>272891; 312331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213624; 252871</t>
+          <t>214450; 253906</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>206944; 236378</t>
+          <t>204205; 236593</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>94160; 125652</t>
+          <t>93078; 124011</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145070; 177426</t>
+          <t>143580; 177929</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104607; 137693</t>
+          <t>104901; 137822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142456; 171615</t>
+          <t>142376; 172504</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>163974; 195235</t>
+          <t>162697; 193674</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>203402; 230343</t>
+          <t>203666; 230371</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>156935; 188694</t>
+          <t>157419; 188303</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>154053; 179278</t>
+          <t>152285; 178385</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>266022; 313372</t>
+          <t>265589; 313349</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>357804; 402188</t>
+          <t>356645; 400236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>270949; 317805</t>
+          <t>271770; 317698</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>302786; 343647</t>
+          <t>304706; 342996</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>213737; 265498</t>
+          <t>214671; 265293</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>320626; 375287</t>
+          <t>318090; 373540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>271691; 326393</t>
+          <t>268743; 322623</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>344960; 404723</t>
+          <t>343935; 406477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>330460; 381332</t>
+          <t>329231; 377489</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>442165; 495810</t>
+          <t>443162; 494117</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>367168; 422350</t>
+          <t>369876; 419204</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>573388; 746463</t>
+          <t>574384; 750678</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>557817; 631661</t>
+          <t>560412; 626134</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>774889; 849521</t>
+          <t>777088; 851981</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>651838; 730661</t>
+          <t>651688; 729115</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>938997; 1195540</t>
+          <t>936183; 1178153</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>304787; 358629</t>
+          <t>303241; 355842</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>295905; 355068</t>
+          <t>294470; 351411</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>349656; 406420</t>
+          <t>348945; 405873</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>119575; 370530</t>
+          <t>118177; 370408</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>414972; 475040</t>
+          <t>415371; 469816</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>458470; 514706</t>
+          <t>454562; 510694</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>500172; 556035</t>
+          <t>501191; 555813</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>346859; 391317</t>
+          <t>347674; 393683</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>735191; 813002</t>
+          <t>736059; 813169</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>767190; 847425</t>
+          <t>766437; 849587</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>862046; 945147</t>
+          <t>863732; 943179</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>397722; 755954</t>
+          <t>386999; 759340</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1273254; 1384974</t>
+          <t>1278406; 1386547</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1667748; 1784240</t>
+          <t>1659947; 1782840</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1633568; 1750301</t>
+          <t>1631591; 1748531</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1310152; 1859567</t>
+          <t>1322592; 1860030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1917351; 2039467</t>
+          <t>1921725; 2034112</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2440594; 2553846</t>
+          <t>2442542; 2556228</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2232652; 2355591</t>
+          <t>2246478; 2364311</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2317771; 2679727</t>
+          <t>2308673; 2627814</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3224177; 3385897</t>
+          <t>3225281; 3389671</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4130658; 4301986</t>
+          <t>4142304; 4302665</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3910385; 4079246</t>
+          <t>3906636; 4069645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3634249; 4375000</t>
+          <t>3690438; 4383430</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,84; 45,41</t>
+          <t>33,4; 45,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,16; 62,85</t>
+          <t>51,19; 63,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,05; 64,44</t>
+          <t>52,24; 64,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,23; 71,15</t>
+          <t>58,03; 69,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,24; 65,11</t>
+          <t>52,3; 65,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,86; 82,5</t>
+          <t>71,53; 82,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,44; 74,46</t>
+          <t>64,0; 74,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,13; 78,82</t>
+          <t>68,04; 76,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,92; 53,39</t>
+          <t>44,91; 53,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,11; 71,11</t>
+          <t>63,12; 71,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59,96; 68,11</t>
+          <t>59,57; 67,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,35; 73,63</t>
+          <t>64,5; 71,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,03; 42,84</t>
+          <t>33,57; 42,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,8; 55,91</t>
+          <t>46,49; 55,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,56; 52,99</t>
+          <t>43,78; 52,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,7; 55,26</t>
+          <t>44,55; 55,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,09; 63,03</t>
+          <t>54,07; 62,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,62; 75,83</t>
+          <t>68,14; 76,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,74; 70,74</t>
+          <t>63,28; 71,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,59; 68,58</t>
+          <t>59,71; 67,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,47; 51,87</t>
+          <t>45,51; 51,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,5; 64,62</t>
+          <t>58,27; 64,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,58; 61,1</t>
+          <t>54,9; 61,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,37; 60,44</t>
+          <t>53,21; 60,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,14; 42,07</t>
+          <t>30,47; 41,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,09; 59,48</t>
+          <t>48,45; 59,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,12; 55,81</t>
+          <t>45,6; 56,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,59; 63,97</t>
+          <t>54,12; 64,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,94; 66,43</t>
+          <t>56,38; 66,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,78; 80,59</t>
+          <t>71,17; 80,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 70,97</t>
+          <t>60,55; 70,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65,11; 73,77</t>
+          <t>66,03; 74,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,21; 52,81</t>
+          <t>45,1; 53,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61,65; 69,15</t>
+          <t>61,51; 68,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,71; 62,08</t>
+          <t>54,43; 62,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,13; 67,66</t>
+          <t>61,28; 68,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,15; 44,87</t>
+          <t>35,09; 45,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,23; 54,32</t>
+          <t>43,1; 53,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,75; 65,96</t>
+          <t>56,24; 66,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,53; 64,75</t>
+          <t>47,5; 61,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,98; 62,85</t>
+          <t>52,97; 62,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,07; 78,66</t>
+          <t>69,68; 78,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,66; 78,76</t>
+          <t>69,75; 78,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,02; 77,96</t>
+          <t>59,29; 69,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,36; 52,75</t>
+          <t>45,71; 52,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,07; 65,25</t>
+          <t>57,82; 65,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64,45; 71,38</t>
+          <t>64,53; 71,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,73; 71,94</t>
+          <t>55,67; 63,86</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,96; 54,05</t>
+          <t>40,32; 54,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,35; 60,57</t>
+          <t>45,98; 60,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,26; 50,15</t>
+          <t>36,21; 50,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,39; 55,06</t>
+          <t>39,7; 51,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,36; 69,93</t>
+          <t>56,55; 70,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,55; 86,05</t>
+          <t>75,73; 86,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,14; 71,05</t>
+          <t>58,12; 71,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,74; 69,19</t>
+          <t>57,3; 67,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,06; 60,09</t>
+          <t>50,55; 60,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,14; 72,26</t>
+          <t>63,11; 72,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,89; 59,07</t>
+          <t>49,25; 58,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,71; 61,07</t>
+          <t>50,59; 58,3</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,37; 45,79</t>
+          <t>34,68; 46,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,4; 64,94</t>
+          <t>52,84; 64,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,87; 52,38</t>
+          <t>39,93; 51,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,8; 63,98</t>
+          <t>51,51; 62,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,49; 69,63</t>
+          <t>58,18; 70,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,96; 82,53</t>
+          <t>72,9; 82,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,64; 68,95</t>
+          <t>56,91; 69,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,24; 69,4</t>
+          <t>59,39; 69,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,38; 57,08</t>
+          <t>48,43; 56,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,48; 72,36</t>
+          <t>64,48; 72,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50,68; 59,25</t>
+          <t>50,63; 59,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57,85; 65,12</t>
+          <t>57,75; 64,81</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,9; 43,14</t>
+          <t>34,93; 42,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,99; 56,36</t>
+          <t>48,18; 56,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,93; 49,14</t>
+          <t>41,0; 49,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,09; 65,11</t>
+          <t>56,97; 65,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,59; 59,15</t>
+          <t>51,92; 59,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,87; 71,21</t>
+          <t>63,88; 71,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,5; 60,64</t>
+          <t>53,11; 60,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,63; 88,39</t>
+          <t>65,86; 72,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,72; 49,96</t>
+          <t>44,75; 50,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,28; 62,8</t>
+          <t>57,25; 62,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48,35; 54,09</t>
+          <t>48,49; 54,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,53; 79,95</t>
+          <t>62,17; 67,57</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,83; 47,91</t>
+          <t>40,57; 47,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,9; 45,23</t>
+          <t>38,13; 45,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,82; 52,13</t>
+          <t>45,05; 52,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,72; 39,88</t>
+          <t>34,17; 41,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,01; 59,96</t>
+          <t>53,02; 60,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,18; 61,99</t>
+          <t>55,21; 61,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,66; 67,28</t>
+          <t>60,63; 67,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,64; 55,07</t>
+          <t>47,44; 53,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,23; 53,28</t>
+          <t>48,1; 53,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,88; 53,07</t>
+          <t>47,68; 52,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53,82; 58,77</t>
+          <t>53,86; 58,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,55; 46,2</t>
+          <t>41,74; 46,44</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39,03; 42,33</t>
+          <t>38,75; 42,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48,51; 52,1</t>
+          <t>48,61; 52,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48,07; 51,51</t>
+          <t>48,05; 51,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38,23; 53,76</t>
+          <t>50,34; 54,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,87; 60,2</t>
+          <t>56,82; 60,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,7; 71,9</t>
+          <t>68,7; 71,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,7</t>
+          <t>63,27; 66,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63,1; 71,83</t>
+          <t>61,94; 64,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48,47; 50,94</t>
+          <t>48,5; 50,86</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59,37; 61,67</t>
+          <t>59,31; 61,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56,3; 58,65</t>
+          <t>56,27; 58,82</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,84; 61,58</t>
+          <t>56,79; 59,15</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201368</t>
+          <t>202842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>216309</t>
+          <t>230530</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>417676</t>
+          <t>433372</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92374; 123987</t>
+          <t>91196; 123024</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>149910; 184168</t>
+          <t>149988; 184903</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155839; 189302</t>
+          <t>153472; 190421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178244; 221576</t>
+          <t>185026; 220033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>136264; 169827</t>
+          <t>136415; 169833</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>206403; 236981</t>
+          <t>205462; 236386</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>183163; 214976</t>
+          <t>184759; 215955</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>200210; 228296</t>
+          <t>215061; 242597</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>239817; 285012</t>
+          <t>239760; 284772</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>366205; 412608</t>
+          <t>366276; 413424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>349229; 396714</t>
+          <t>346988; 395680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>392811; 442599</t>
+          <t>409539; 455333</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>256633</t>
+          <t>263538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>332540</t>
+          <t>346257</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>589173</t>
+          <t>609794</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>167795; 211242</t>
+          <t>165543; 210895</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>236584; 282648</t>
+          <t>235044; 280974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218938; 266306</t>
+          <t>220009; 266040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>226551; 286477</t>
+          <t>236387; 296430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>272596; 317656</t>
+          <t>272497; 314948</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>353452; 396379</t>
+          <t>356178; 398272</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>328196; 370044</t>
+          <t>330988; 373054</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>311624; 352711</t>
+          <t>325898; 367911</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>453334; 517113</t>
+          <t>453759; 517779</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>601505; 664426</t>
+          <t>599210; 663034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>559791; 626653</t>
+          <t>563080; 629560</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>551150; 624153</t>
+          <t>572796; 648149</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>187762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>242728</t>
+          <t>250083</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>427709</t>
+          <t>437846</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99288; 134150</t>
+          <t>97139; 132851</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>155386; 192176</t>
+          <t>156536; 193315</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143737; 177781</t>
+          <t>145273; 180062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166216; 202176</t>
+          <t>171011; 205235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>187622; 222820</t>
+          <t>189097; 222511</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>241378; 274814</t>
+          <t>242692; 275033</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>201273; 238682</t>
+          <t>203647; 237762</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>227317; 257553</t>
+          <t>235308; 264606</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>295779; 345533</t>
+          <t>295064; 347158</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>409437; 459226</t>
+          <t>408491; 457089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>358253; 406537</t>
+          <t>356420; 407462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>399940; 450086</t>
+          <t>412014; 458707</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179212</t>
+          <t>203117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>313004</t>
+          <t>272099</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>492215</t>
+          <t>475216</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126058; 160936</t>
+          <t>125847; 162770</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165406; 203138</t>
+          <t>161201; 201471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206268; 244027</t>
+          <t>208083; 245890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>154811; 202382</t>
+          <t>177227; 229414</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>196805; 233454</t>
+          <t>196771; 233567</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>271872; 305170</t>
+          <t>270330; 305511</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>269780; 305037</t>
+          <t>270143; 304110</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>252209; 370893</t>
+          <t>250196; 291434</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>331156; 385107</t>
+          <t>333717; 386014</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>442434; 497207</t>
+          <t>440546; 498953</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>488019; 540540</t>
+          <t>488629; 541337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>431461; 567050</t>
+          <t>442610; 507777</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86506</t>
+          <t>93995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>134635</t>
+          <t>141831</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>221141</t>
+          <t>235825</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81248; 109889</t>
+          <t>81980; 110263</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98542; 128783</t>
+          <t>97766; 128507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76588; 105933</t>
+          <t>76492; 105721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75764; 98414</t>
+          <t>81649; 105855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>117049; 145216</t>
+          <t>117441; 145944</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>165906; 188964</t>
+          <t>166303; 190497</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>127096; 155301</t>
+          <t>127048; 155336</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124643; 144370</t>
+          <t>130187; 152369</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>205753; 246946</t>
+          <t>207754; 247753</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>272891; 312331</t>
+          <t>272749; 311925</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214450; 253906</t>
+          <t>211692; 251355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>204205; 236593</t>
+          <t>219009; 252373</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157496</t>
+          <t>155536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>166210</t>
+          <t>170963</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>323706</t>
+          <t>326500</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>93078; 124011</t>
+          <t>93924; 126685</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>143580; 177929</t>
+          <t>144765; 177438</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104901; 137822</t>
+          <t>105057; 136592</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142376; 172504</t>
+          <t>139440; 170097</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>162697; 193674</t>
+          <t>161831; 194789</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>203666; 230371</t>
+          <t>203501; 230706</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>157419; 188303</t>
+          <t>155434; 188651</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>152285; 178385</t>
+          <t>156649; 183037</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>265589; 313349</t>
+          <t>265864; 312212</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>356645; 400236</t>
+          <t>356647; 399576</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>271770; 317698</t>
+          <t>271502; 316815</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>304706; 342996</t>
+          <t>308639; 346384</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>375182</t>
+          <t>439105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>648576</t>
+          <t>533045</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1023758</t>
+          <t>972150</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>214671; 265293</t>
+          <t>214856; 261653</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>318090; 373540</t>
+          <t>319349; 372613</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>268743; 322623</t>
+          <t>269194; 323365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>343935; 406477</t>
+          <t>410016; 468995</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>329231; 377489</t>
+          <t>331374; 378638</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>443162; 494117</t>
+          <t>443223; 494705</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>369876; 419204</t>
+          <t>367161; 420460</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>574384; 750678</t>
+          <t>508487; 558830</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>560412; 626134</t>
+          <t>560795; 630917</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>777088; 851981</t>
+          <t>776679; 848812</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>651688; 729115</t>
+          <t>653609; 731612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>936183; 1178153</t>
+          <t>927474; 1007963</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264248</t>
+          <t>299402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>368952</t>
+          <t>419769</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>633200</t>
+          <t>719171</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>303241; 355842</t>
+          <t>301334; 356459</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>294470; 351411</t>
+          <t>296266; 352390</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>348945; 405873</t>
+          <t>350765; 405844</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>118177; 370408</t>
+          <t>272673; 331419</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>415371; 469816</t>
+          <t>415455; 471455</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>454562; 510694</t>
+          <t>454856; 510345</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>501191; 555813</t>
+          <t>500904; 556117</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>347674; 393683</t>
+          <t>393790; 445772</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>736059; 813169</t>
+          <t>734146; 813679</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>766437; 849587</t>
+          <t>763272; 846675</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>863732; 943179</t>
+          <t>864339; 944374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>386999; 759340</t>
+          <t>679487; 756090</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1705627</t>
+          <t>1845298</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2422952</t>
+          <t>2364576</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4128578</t>
+          <t>4209874</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1278406; 1386547</t>
+          <t>1269227; 1384329</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1659947; 1782840</t>
+          <t>1663558; 1785559</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1631591; 1748531</t>
+          <t>1631125; 1744987</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1322592; 1860030</t>
+          <t>1778416; 1909063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1921725; 2034112</t>
+          <t>1919943; 2033055</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2442542; 2556228</t>
+          <t>2442617; 2556595</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2246478; 2364311</t>
+          <t>2242521; 2360411</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2308673; 2627814</t>
+          <t>2312258; 2418038</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3225281; 3389671</t>
+          <t>3227741; 3384674</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4142304; 4302665</t>
+          <t>4138554; 4304306</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3906636; 4069645</t>
+          <t>3904331; 4081280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3690438; 4383430</t>
+          <t>4126631; 4298084</t>
         </is>
       </c>
     </row>
